--- a/data/isx_xlsx/JBTM.IC.xlsx
+++ b/data/isx_xlsx/JBTM.IC.xlsx
@@ -11252,11 +11252,26 @@
       <c r="P42" s="16">
         <v>745.28</v>
       </c>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="15"/>
+      <c r="Q42" s="17">
+        <f t="shared" ref="Q42:U42" si="1">SUM(Q43:Q47)</f>
+        <v>749.26</v>
+      </c>
+      <c r="R42" s="17">
+        <f t="shared" si="1"/>
+        <v>732.86</v>
+      </c>
+      <c r="S42" s="17">
+        <f t="shared" si="1"/>
+        <v>831.36</v>
+      </c>
+      <c r="T42" s="17">
+        <f t="shared" si="1"/>
+        <v>689.12</v>
+      </c>
+      <c r="U42" s="17">
+        <f t="shared" si="1"/>
+        <v>746.68</v>
+      </c>
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">

--- a/data/isx_xlsx/JBTM.IC.xlsx
+++ b/data/isx_xlsx/JBTM.IC.xlsx
@@ -13596,10 +13596,16 @@
       <c r="P91" s="17">
         <v>26.3</v>
       </c>
-      <c r="Q91" s="15"/>
-      <c r="R91" s="15"/>
-      <c r="S91" s="15"/>
-      <c r="T91" s="15"/>
+      <c r="Q91" s="17">
+        <v>9.9</v>
+      </c>
+      <c r="R91" s="17">
+        <v>2.32</v>
+      </c>
+      <c r="S91" s="17">
+        <v>4.17</v>
+      </c>
+      <c r="T91" s="16"/>
       <c r="U91" s="15"/>
     </row>
     <row r="92" ht="15.0" customHeight="1">
